--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62306.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62306.xlsx
@@ -702,6 +702,9 @@
       <c r="J4" t="n">
         <v>3.35</v>
       </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62306.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62306.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lc</t>
+          <t>Lilicic n</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DlkLiult</t>
+          <t>NLOKLI T</t>
         </is>
       </c>
     </row>
